--- a/results/Int Task Remove ACC -0.9/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_9_permute.xlsx
@@ -440,127 +440,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6302638468406179</v>
+        <v>0.6221646785572837</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6333581147755574</v>
+        <v>0.6128912726808934</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6328967771818298</v>
+        <v>0.5988319717525123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.633824151333499</v>
+        <v>0.6058406446978901</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6235394612301888</v>
+        <v>0.6191637186260228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6233157569695709</v>
+        <v>0.6300728675093477</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.619857990588646</v>
+        <v>0.6348960186347495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6184459518423295</v>
+        <v>0.6497475984936463</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6192894159187482</v>
+        <v>0.6545568205465566</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6324258738395236</v>
+        <v>0.6568076244050776</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6347139337714558</v>
+        <v>0.6345563506501353</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6442763259470091</v>
+        <v>0.6312664044197115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6552646859413703</v>
+        <v>0.6451020010874746</v>
       </c>
     </row>
     <row r="15">
@@ -570,107 +570,107 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6676743147903255</v>
+        <v>0.6648559431828098</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6616442011425197</v>
+        <v>0.666095462814411</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6621661218105781</v>
+        <v>0.6651914156636616</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6619657445508798</v>
+        <v>0.6651914156636616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6704983922829582</v>
+        <v>0.6521992830723171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6729774315461606</v>
+        <v>0.6412015251495278</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6672549322342232</v>
+        <v>0.6459454651638932</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6675158925682525</v>
+        <v>0.6459874202015184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6436565661312085</v>
+        <v>0.6472316387973337</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6412473400506146</v>
+        <v>0.6346541897978775</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6341735528868422</v>
+        <v>0.6346541897978775</v>
       </c>
     </row>
     <row r="26">
@@ -680,647 +680,647 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6807089058797469</v>
+        <v>0.640558606152958</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6782063717954743</v>
+        <v>0.6080875886929495</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6378135719512112</v>
+        <v>0.6182977666494371</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6431494136363942</v>
+        <v>0.6249431089689801</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6327064691311615</v>
+        <v>0.5928032006659103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6304370372359349</v>
+        <v>0.6045464156972256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6301760769019058</v>
+        <v>0.6032322160986514</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6236893246245864</v>
+        <v>0.616019440286234</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6204552625042794</v>
+        <v>0.5825282441313293</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5780627177466453</v>
+        <v>0.60347958300049</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5780627177466453</v>
+        <v>0.6120773449509629</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5780627177466453</v>
+        <v>0.6120773449509629</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5780627177466453</v>
+        <v>0.6047238015963052</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.574167108593063</v>
+        <v>0.606107814377488</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5808681672025724</v>
+        <v>0.6045047962999013</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5905748847075567</v>
+        <v>0.5889404842618262</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5702760305835443</v>
+        <v>0.5924308077519483</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5887719928307231</v>
+        <v>0.5891873477032135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.587695594385409</v>
+        <v>0.5888611053306393</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5894244775758715</v>
+        <v>0.6094026273922762</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.604523088696306</v>
+        <v>0.6358433633843283</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5906690318119877</v>
+        <v>0.6415333055870684</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5789164188522444</v>
+        <v>0.6466640710483389</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.596223710973424</v>
+        <v>0.6431735797380663</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5904313984788782</v>
+        <v>0.6441333431787821</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5870996650309797</v>
+        <v>0.6280373769039196</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5419350670273682</v>
+        <v>0.635940699071619</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5443723190730958</v>
+        <v>0.6379677986695219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5441113587390666</v>
+        <v>0.6405680040813861</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5886843907121616</v>
+        <v>0.6490310064510066</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5822954775825843</v>
+        <v>0.6274273506568481</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5915036014204298</v>
+        <v>0.6274273506568481</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5881344440789694</v>
+        <v>0.6254886922782592</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5913404802341427</v>
+        <v>0.642143667474441</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6345387295343327</v>
+        <v>0.5611857164913505</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6116022461048943</v>
+        <v>0.5507333740576899</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6187505454154891</v>
+        <v>0.5551883277728923</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6236529076519275</v>
+        <v>0.5638792299068934</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.612152024917936</v>
+        <v>0.5181739153783673</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6102833475421061</v>
+        <v>0.5188962133061241</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6104837248018045</v>
+        <v>0.5241340480234142</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5693545301371427</v>
+        <v>0.523873087689385</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.568194221616578</v>
+        <v>0.5058575945330908</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5390832992099027</v>
+        <v>0.5016449731152119</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5328994623042378</v>
+        <v>0.5011230524471535</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5437666561499372</v>
+        <v>0.4997576677026764</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5394328685833966</v>
+        <v>0.499012042774</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5383890272472797</v>
+        <v>0.5001770502587787</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.535201619128812</v>
+        <v>0.5001350952211534</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5283513684055072</v>
+        <v>0.5079592062778162</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5229317844652243</v>
+        <v>0.5080384173888527</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5213240674234236</v>
+        <v>0.5070737871637723</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5282023441118622</v>
+        <v>0.5056850754183756</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5237054353590345</v>
+        <v>0.507092415200478</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5200286636817056</v>
+        <v>0.5075957078318307</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5165569682282891</v>
+        <v>0.5078566681658599</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5158952533748632</v>
+        <v>0.510265894246454</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.507101813128906</v>
+        <v>0.5105268545804832</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.5103451053574906</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.5176286677093892</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.5176286677093892</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5012391839913002</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5012391839913002</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.499174828319986</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.4989277970584484</v>
       </c>
     </row>
   </sheetData>
